--- a/sources/prototype_step4.xlsx
+++ b/sources/prototype_step4.xlsx
@@ -696,6 +696,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
@@ -748,6 +753,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
@@ -795,6 +805,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
@@ -840,6 +855,11 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -5151,6 +5171,11 @@
       <c r="J99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">

--- a/sources/prototype_step4.xlsx
+++ b/sources/prototype_step4.xlsx
@@ -4285,6 +4285,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -4392,6 +4397,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
